--- a/OIA - Development Components.xlsx
+++ b/OIA - Development Components.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bharathm/BisonTransport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9925496-F92E-DF4B-BFE6-C816419F5890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6571EE9-402D-D148-B1C5-18DFC3772CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{AACD329B-91F4-2544-9EE2-8DA722C7E980}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{AACD329B-91F4-2544-9EE2-8DA722C7E980}"/>
   </bookViews>
   <sheets>
     <sheet name="OIA" sheetId="1" r:id="rId1"/>
+    <sheet name="Tech Stack" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="198">
   <si>
     <t>Database Tables: 14</t>
   </si>
@@ -330,13 +331,316 @@
   </si>
   <si>
     <t>80+</t>
+  </si>
+  <si>
+    <t>Tech Stack — Order Intelligence Platform</t>
+  </si>
+  <si>
+    <t>Backend (Agents + API)</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Python 3.12</t>
+  </si>
+  <si>
+    <t>API Framework</t>
+  </si>
+  <si>
+    <t>FastAPI (async)</t>
+  </si>
+  <si>
+    <t>ORM / Migrations</t>
+  </si>
+  <si>
+    <t>SQLAlchemy 2.0 (async) + Alembic</t>
+  </si>
+  <si>
+    <t>Data Models</t>
+  </si>
+  <si>
+    <t>Pydantic v2</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>PostgreSQL 16 + pgvector extension</t>
+  </si>
+  <si>
+    <t>Cache</t>
+  </si>
+  <si>
+    <t>Redis 7</t>
+  </si>
+  <si>
+    <t>Message Queue</t>
+  </si>
+  <si>
+    <t>ElasticMQ (local) / Amazon SQS (cloud)</t>
+  </si>
+  <si>
+    <t>Object Storage</t>
+  </si>
+  <si>
+    <t>MinIO (local) / Amazon S3 (cloud)</t>
+  </si>
+  <si>
+    <t>Email Inbound</t>
+  </si>
+  <si>
+    <t>Microsoft 365 Graph API</t>
+  </si>
+  <si>
+    <t>Email Outbound</t>
+  </si>
+  <si>
+    <t>Microsoft 365 Graph API (production) / Mailpit (local)</t>
+  </si>
+  <si>
+    <t>LLM</t>
+  </si>
+  <si>
+    <t>OpenAI GPT-4o (extraction) + GPT-4o-mini (classification)</t>
+  </si>
+  <si>
+    <t>OCR / PDF</t>
+  </si>
+  <si>
+    <t>pdfplumber + pytesseract + Pillow</t>
+  </si>
+  <si>
+    <t>Excel Parsing</t>
+  </si>
+  <si>
+    <t>openpyxl</t>
+  </si>
+  <si>
+    <t>Word Parsing</t>
+  </si>
+  <si>
+    <t>python-docx</t>
+  </si>
+  <si>
+    <t>HTTP Client</t>
+  </si>
+  <si>
+    <t>httpx (async)</t>
+  </si>
+  <si>
+    <t>JWT (python-jose)</t>
+  </si>
+  <si>
+    <t>Frontend</t>
+  </si>
+  <si>
+    <t>Framework</t>
+  </si>
+  <si>
+    <t>React 18</t>
+  </si>
+  <si>
+    <t>TypeScript (strict mode)</t>
+  </si>
+  <si>
+    <t>Build Tool</t>
+  </si>
+  <si>
+    <t>Vite</t>
+  </si>
+  <si>
+    <t>Styling</t>
+  </si>
+  <si>
+    <t>Tailwind CSS v3</t>
+  </si>
+  <si>
+    <t>Data Fetching</t>
+  </si>
+  <si>
+    <t>TanStack React Query v5</t>
+  </si>
+  <si>
+    <t>Routing</t>
+  </si>
+  <si>
+    <t>React Router v6</t>
+  </si>
+  <si>
+    <t>Charts</t>
+  </si>
+  <si>
+    <t>Recharts</t>
+  </si>
+  <si>
+    <t>PDF Viewer</t>
+  </si>
+  <si>
+    <t>PDF.js</t>
+  </si>
+  <si>
+    <t>Rich Text</t>
+  </si>
+  <si>
+    <t>TipTap</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Containerization</t>
+  </si>
+  <si>
+    <t>Docker + Docker Compose</t>
+  </si>
+  <si>
+    <t>Local Queue</t>
+  </si>
+  <si>
+    <t>ElasticMQ (SQS-compatible)</t>
+  </si>
+  <si>
+    <t>Local Storage</t>
+  </si>
+  <si>
+    <t>MinIO (S3-compatible)</t>
+  </si>
+  <si>
+    <t>Local Email</t>
+  </si>
+  <si>
+    <t>Mailpit (SMTP capture)</t>
+  </si>
+  <si>
+    <t>pgvector/pgvector:pg16</t>
+  </si>
+  <si>
+    <t>Adapter Pattern</t>
+  </si>
+  <si>
+    <t>Swap local ↔ AWS via ADAPTER_MODE env var</t>
+  </si>
+  <si>
+    <t>IaC (planned)</t>
+  </si>
+  <si>
+    <t>AWS CDK (TypeScript)</t>
+  </si>
+  <si>
+    <t>Cloud (Phase 1 — planned)</t>
+  </si>
+  <si>
+    <t>Compute</t>
+  </si>
+  <si>
+    <t>AWS ECS Fargate</t>
+  </si>
+  <si>
+    <t>Amazon RDS PostgreSQL Multi-AZ</t>
+  </si>
+  <si>
+    <t>Amazon ElastiCache Redis</t>
+  </si>
+  <si>
+    <t>Queue</t>
+  </si>
+  <si>
+    <t>Amazon SQS</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Amazon S3</t>
+  </si>
+  <si>
+    <t>AWS SES</t>
+  </si>
+  <si>
+    <t>AWS Bedrock (Claude)</t>
+  </si>
+  <si>
+    <t>OCR</t>
+  </si>
+  <si>
+    <t>AWS Textract</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Amazon EventBridge</t>
+  </si>
+  <si>
+    <t>Amazon Cognito</t>
+  </si>
+  <si>
+    <t>CDN</t>
+  </si>
+  <si>
+    <t>Amazon CloudFront</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>CloudWatch + X-Ray</t>
+  </si>
+  <si>
+    <t>DevOps &amp; Tooling</t>
+  </si>
+  <si>
+    <t>Version Control</t>
+  </si>
+  <si>
+    <t>Git + GitHub</t>
+  </si>
+  <si>
+    <t>IDE</t>
+  </si>
+  <si>
+    <t>Kiro (AI-powered VS Code)</t>
+  </si>
+  <si>
+    <t>Python Linting</t>
+  </si>
+  <si>
+    <t>Ruff + Black + isort + mypy</t>
+  </si>
+  <si>
+    <t>JS/TS Linting</t>
+  </si>
+  <si>
+    <t>ESLint + Prettier</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>pytest + Vitest + Playwright</t>
+  </si>
+  <si>
+    <t>Pre-commit</t>
+  </si>
+  <si>
+    <t>pre-commit hooks</t>
+  </si>
+  <si>
+    <t>PDF Generation</t>
+  </si>
+  <si>
+    <t>fpdf2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -353,6 +657,12 @@
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -379,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -391,9 +701,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -402,6 +709,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -746,20 +1058,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
@@ -918,17 +1230,17 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1005,20 +1317,20 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1100,11 +1412,11 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
@@ -1184,17 +1496,17 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1271,4 +1583,497 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72105D6-573C-3F43-9EF8-5BB6254D37B0}">
+  <dimension ref="A1:B62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>